--- a/data/overtheyears.xlsx
+++ b/data/overtheyears.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\efspieurope\workshop\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7386A4E8-5B3B-487C-9282-F10FC3B4197F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A89B87-32FB-4A09-9C7F-A0C5D756D808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -498,19 +498,19 @@
         <v>2026</v>
       </c>
       <c r="B7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C7">
-        <v>331</v>
+        <v>414</v>
       </c>
       <c r="D7">
         <v>31</v>
       </c>
       <c r="E7">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F7">
-        <v>183</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
